--- a/Databases/Database3Clean/Winter Birds '15 Clean.xlsx
+++ b/Databases/Database3Clean/Winter Birds '15 Clean.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohanpoudel/Documents/USFWS/PipingPlover/Databases/Database3Clean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35CB940-82B0-6E4C-A9D3-5B7154F9CFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0D75B0-E175-8D4B-B42B-B49E8F711B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4560" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA SHEET 1" sheetId="1" r:id="rId1"/>
@@ -1594,9 +1594,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1711,16 +1711,16 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1729,7 +1729,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1741,19 +1741,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1762,18 +1762,18 @@
     <xf numFmtId="14" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2084,7 +2084,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R658"/>
+  <dimension ref="A2:R659"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="23" customWidth="1"/>
@@ -2102,124 +2102,74 @@
     <col min="17" max="18" width="17.33203125" style="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="63" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="24" t="s">
+    <row r="2" spans="1:16" ht="63" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="11">
-        <v>42046</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="5">
-        <v>30.05275</v>
-      </c>
-      <c r="G3" s="5">
-        <v>-85.600409999999997</v>
-      </c>
-      <c r="H3" s="5">
-        <v>30.08897</v>
-      </c>
-      <c r="I3" s="6">
-        <v>-85.678669999999997</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="2">
-        <v>3</v>
-      </c>
-      <c r="M3" s="6">
-        <v>30.06503</v>
-      </c>
-      <c r="N3" s="6">
-        <v>-85.617720000000006</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2257,116 +2207,119 @@
         <v>22</v>
       </c>
       <c r="L4" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" s="6">
-        <v>30.066050000000001</v>
+        <v>30.06503</v>
       </c>
       <c r="N4" s="6">
-        <v>-85.617199999999997</v>
+        <v>-85.617720000000006</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="11">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="5">
-        <v>30.02046</v>
+        <v>30.05275</v>
       </c>
       <c r="G5" s="5">
-        <v>30.02046</v>
+        <v>-85.600409999999997</v>
       </c>
       <c r="H5" s="5">
-        <v>30.02046</v>
-      </c>
-      <c r="I5" s="5">
-        <v>30.02046</v>
+        <v>30.08897</v>
+      </c>
+      <c r="I5" s="6">
+        <v>-85.678669999999997</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="L5" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5" s="6">
-        <v>29.99042</v>
+        <v>30.066050000000001</v>
       </c>
       <c r="N5" s="6">
-        <v>-85.504760000000005</v>
+        <v>-85.617199999999997</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="11">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F6" s="5">
-        <v>25.947458999999998</v>
+        <v>30.02046</v>
       </c>
       <c r="G6" s="5">
-        <v>-81.743350000000007</v>
+        <v>30.02046</v>
       </c>
       <c r="H6" s="5">
-        <v>25.967960000000001</v>
-      </c>
-      <c r="I6" s="6">
-        <v>-81.744190000000003</v>
+        <v>30.02046</v>
+      </c>
+      <c r="I6" s="5">
+        <v>30.02046</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L6" s="2">
         <v>1</v>
       </c>
       <c r="M6" s="6">
-        <v>25.9512</v>
+        <v>29.99042</v>
       </c>
       <c r="N6" s="6">
-        <v>-81.750309999999999</v>
+        <v>-85.504760000000005</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2377,7 +2330,7 @@
         <v>34</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>36</v>
@@ -2386,7 +2339,7 @@
         <v>37</v>
       </c>
       <c r="F7" s="5">
-        <v>25.94746</v>
+        <v>25.947458999999998</v>
       </c>
       <c r="G7" s="5">
         <v>-81.743350000000007</v>
@@ -2404,16 +2357,16 @@
         <v>39</v>
       </c>
       <c r="L7" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M7" s="6">
-        <v>25.954830000000001</v>
+        <v>25.9512</v>
       </c>
       <c r="N7" s="6">
-        <v>-81.751639999999995</v>
+        <v>-81.750309999999999</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2421,49 +2374,46 @@
         <v>42045</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F8" s="5">
-        <v>30.486388900000001</v>
+        <v>25.94746</v>
       </c>
       <c r="G8" s="5">
-        <v>-81.441111100000001</v>
+        <v>-81.743350000000007</v>
       </c>
       <c r="H8" s="5">
-        <v>30.429444400000001</v>
+        <v>25.967960000000001</v>
       </c>
       <c r="I8" s="6">
-        <v>-81.409722200000004</v>
+        <v>-81.744190000000003</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="L8" s="2">
         <v>4</v>
       </c>
       <c r="M8" s="6">
-        <v>30.470555600000001</v>
+        <v>25.954830000000001</v>
       </c>
       <c r="N8" s="6">
-        <v>-81.412222200000002</v>
+        <v>-81.751639999999995</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2501,13 +2451,13 @@
         <v>48</v>
       </c>
       <c r="L9" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M9" s="6">
-        <v>30.4327778</v>
+        <v>30.470555600000001</v>
       </c>
       <c r="N9" s="6">
-        <v>-81.406388899999996</v>
+        <v>-81.412222200000002</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>49</v>
@@ -2551,16 +2501,16 @@
         <v>48</v>
       </c>
       <c r="L10" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M10" s="6">
-        <v>30.431111099999999</v>
+        <v>30.4327778</v>
       </c>
       <c r="N10" s="6">
-        <v>-81.4069444</v>
+        <v>-81.406388899999996</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>50</v>
@@ -2568,102 +2518,102 @@
     </row>
     <row r="11" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="11">
-        <v>42041</v>
+        <v>42045</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="5">
-        <v>30.411283000000001</v>
+        <v>30.486388900000001</v>
       </c>
       <c r="G11" s="5">
-        <v>-81.414028999999999</v>
+        <v>-81.441111100000001</v>
       </c>
       <c r="H11" s="5">
-        <v>30.408284999999999</v>
+        <v>30.429444400000001</v>
       </c>
       <c r="I11" s="6">
-        <v>-81.414028999999999</v>
+        <v>-81.409722200000004</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="L11" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M11" s="6">
-        <v>30.420041000000001</v>
+        <v>30.431111099999999</v>
       </c>
       <c r="N11" s="6">
-        <v>-81.410471999999999</v>
+        <v>-81.4069444</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="11">
-        <v>42046</v>
+        <v>42041</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F12" s="5">
-        <v>30.37453</v>
+        <v>30.411283000000001</v>
       </c>
       <c r="G12" s="5">
-        <v>-86.918970000000002</v>
+        <v>-81.414028999999999</v>
       </c>
       <c r="H12" s="5">
-        <v>30.357500000000002</v>
+        <v>30.408284999999999</v>
       </c>
       <c r="I12" s="6">
-        <v>-87.04365</v>
+        <v>-81.414028999999999</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="L12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="6">
-        <v>30.369219999999999</v>
+        <v>30.420041000000001</v>
       </c>
       <c r="N12" s="6">
-        <v>-86.955020000000005</v>
+        <v>-81.410471999999999</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2701,19 +2651,19 @@
         <v>64</v>
       </c>
       <c r="L13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="6">
-        <v>30.357500000000002</v>
+        <v>30.369219999999999</v>
       </c>
       <c r="N13" s="6">
-        <v>-87.04365</v>
+        <v>-86.955020000000005</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2721,99 +2671,99 @@
         <v>42046</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F14" s="5">
-        <v>29.681170000000002</v>
+        <v>30.37453</v>
       </c>
       <c r="G14" s="5">
-        <v>-85.21696</v>
+        <v>-86.918970000000002</v>
       </c>
       <c r="H14" s="5">
-        <v>29.673760000000001</v>
+        <v>30.357500000000002</v>
       </c>
       <c r="I14" s="6">
-        <v>-85.074969999999993</v>
+        <v>-87.04365</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L14" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M14" s="6">
-        <v>29.643419999999999</v>
+        <v>30.357500000000002</v>
       </c>
       <c r="N14" s="6">
-        <v>-85.15213</v>
+        <v>-87.04365</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="11">
-        <v>42042</v>
+        <v>42046</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F15" s="5">
-        <v>29.90457</v>
+        <v>29.681170000000002</v>
       </c>
       <c r="G15" s="5">
-        <v>-84.424199999999999</v>
+        <v>-85.21696</v>
       </c>
       <c r="H15" s="5">
-        <v>29.918959999999998</v>
+        <v>29.673760000000001</v>
       </c>
       <c r="I15" s="6">
-        <v>-84.441199999999995</v>
+        <v>-85.074969999999993</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L15" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M15" s="6">
-        <v>29.90897</v>
+        <v>29.643419999999999</v>
       </c>
       <c r="N15" s="6">
-        <v>-84.434569999999994</v>
+        <v>-85.15213</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2851,116 +2801,116 @@
         <v>80</v>
       </c>
       <c r="L16" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M16" s="6">
-        <v>29.914339999999999</v>
+        <v>29.90897</v>
       </c>
       <c r="N16" s="6">
-        <v>-84.440939999999998</v>
+        <v>-84.434569999999994</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="11">
-        <v>42047</v>
+        <v>42042</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F17" s="5">
-        <v>29.682300000000001</v>
+        <v>29.90457</v>
       </c>
       <c r="G17" s="5">
-        <v>-84.797349999999994</v>
+        <v>-84.424199999999999</v>
       </c>
       <c r="H17" s="5">
-        <v>29.77214</v>
+        <v>29.918959999999998</v>
       </c>
       <c r="I17" s="6">
-        <v>-84.695509999999999</v>
+        <v>-84.441199999999995</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="L17" s="2">
         <v>7</v>
       </c>
       <c r="M17" s="6">
-        <v>29.748339999999999</v>
+        <v>29.914339999999999</v>
       </c>
       <c r="N17" s="6">
-        <v>-84.71011</v>
+        <v>-84.440939999999998</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="11">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="5">
-        <v>29.832249999999998</v>
+        <v>29.682300000000001</v>
       </c>
       <c r="G18" s="5">
-        <v>-84.574650000000005</v>
+        <v>-84.797349999999994</v>
       </c>
       <c r="H18" s="5">
-        <v>29.78659</v>
+        <v>29.77214</v>
       </c>
       <c r="I18" s="6">
-        <v>-84.674480000000003</v>
+        <v>-84.695509999999999</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L18" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M18" s="6">
-        <v>29.781700000000001</v>
+        <v>29.748339999999999</v>
       </c>
       <c r="N18" s="6">
-        <v>-84.651539999999997</v>
+        <v>-84.71011</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2998,69 +2948,69 @@
         <v>94</v>
       </c>
       <c r="L19" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M19" s="6">
-        <v>29.789249999999999</v>
+        <v>29.781700000000001</v>
       </c>
       <c r="N19" s="6">
-        <v>-84.641620000000003</v>
+        <v>-84.651539999999997</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="13">
-        <v>42047</v>
+      <c r="A20" s="11">
+        <v>42046</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="7">
-        <v>29.640920000000001</v>
-      </c>
-      <c r="G20" s="7">
-        <v>-85.155739999999994</v>
-      </c>
-      <c r="H20" s="7">
-        <v>29.632280000000002</v>
-      </c>
-      <c r="I20" s="5">
-        <v>-85.156779999999998</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>101</v>
+      <c r="F20" s="5">
+        <v>29.832249999999998</v>
+      </c>
+      <c r="G20" s="5">
+        <v>-84.574650000000005</v>
+      </c>
+      <c r="H20" s="5">
+        <v>29.78659</v>
+      </c>
+      <c r="I20" s="6">
+        <v>-84.674480000000003</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="L20" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M20" s="6">
-        <v>29.641639999999999</v>
+        <v>29.789249999999999</v>
       </c>
       <c r="N20" s="6">
-        <v>-85.155330000000006</v>
+        <v>-84.641620000000003</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3068,51 +3018,54 @@
         <v>42047</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F21" s="7">
-        <v>29.471430000000002</v>
+        <v>29.640920000000001</v>
       </c>
       <c r="G21" s="7">
-        <v>-84.460890000000006</v>
+        <v>-85.155739999999994</v>
       </c>
       <c r="H21" s="7">
-        <v>29.793510000000001</v>
+        <v>29.632280000000002</v>
       </c>
       <c r="I21" s="5">
-        <v>-84.74915</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>107</v>
+        <v>-85.156779999999998</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L21" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M21" s="6">
-        <v>29.471430000000002</v>
+        <v>29.641639999999999</v>
       </c>
       <c r="N21" s="6">
-        <v>-84.460890000000006</v>
+        <v>-85.155330000000006</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="13">
-        <v>42046</v>
+        <v>42047</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>104</v>
@@ -3121,40 +3074,40 @@
         <v>105</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F22" s="7">
-        <v>29.869420000000002</v>
+        <v>29.471430000000002</v>
       </c>
       <c r="G22" s="7">
-        <v>-84.594139999999996</v>
+        <v>-84.460890000000006</v>
       </c>
       <c r="H22" s="7">
-        <v>29.523250000000001</v>
+        <v>29.793510000000001</v>
       </c>
       <c r="I22" s="5">
-        <v>-84.352119999999999</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>111</v>
+        <v>-84.74915</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L22" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M22" s="6">
-        <v>29.52505</v>
+        <v>29.471430000000002</v>
       </c>
       <c r="N22" s="6">
-        <v>-84.343969999999999</v>
+        <v>-84.460890000000006</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3192,66 +3145,63 @@
         <v>112</v>
       </c>
       <c r="L23" s="2">
+        <v>9</v>
+      </c>
+      <c r="M23" s="6">
+        <v>29.52505</v>
+      </c>
+      <c r="N23" s="6">
+        <v>-84.343969999999999</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="13">
+        <v>42046</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="7">
+        <v>29.869420000000002</v>
+      </c>
+      <c r="G24" s="7">
+        <v>-84.594139999999996</v>
+      </c>
+      <c r="H24" s="7">
+        <v>29.523250000000001</v>
+      </c>
+      <c r="I24" s="5">
+        <v>-84.352119999999999</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L24" s="2">
         <v>11</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M24" s="6">
         <v>29.523250000000001</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N24" s="6">
         <v>-84.352119999999999</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="4">
-        <v>42041</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" s="2">
-        <v>29.8794</v>
-      </c>
-      <c r="G24" s="2">
-        <v>-85.384739999999994</v>
-      </c>
-      <c r="H24" s="2">
-        <v>29.759229999999999</v>
-      </c>
-      <c r="I24" s="6">
-        <v>-85.40343</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L24" s="2">
-        <v>2</v>
-      </c>
-      <c r="M24" s="6">
-        <v>29.829070000000002</v>
-      </c>
-      <c r="N24" s="6">
-        <v>-85.410449999999997</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3289,19 +3239,19 @@
         <v>117</v>
       </c>
       <c r="L25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25" s="6">
-        <v>29.845140000000001</v>
+        <v>29.829070000000002</v>
       </c>
       <c r="N25" s="6">
-        <v>-85.403409999999994</v>
+        <v>-85.410449999999997</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3339,69 +3289,69 @@
         <v>117</v>
       </c>
       <c r="L26" s="2">
+        <v>3</v>
+      </c>
+      <c r="M26" s="6">
+        <v>29.845140000000001</v>
+      </c>
+      <c r="N26" s="6">
+        <v>-85.403409999999994</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="4">
+        <v>42041</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="2">
+        <v>29.8794</v>
+      </c>
+      <c r="G27" s="2">
+        <v>-85.384739999999994</v>
+      </c>
+      <c r="H27" s="2">
+        <v>29.759229999999999</v>
+      </c>
+      <c r="I27" s="6">
+        <v>-85.40343</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L27" s="2">
         <v>5</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M27" s="6">
         <v>29.843699999999998</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N27" s="6">
         <v>-85.415629999999993</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="11">
-        <v>42045</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F27" s="5">
-        <v>29.683039999999998</v>
-      </c>
-      <c r="G27" s="5">
-        <v>-85.222189999999998</v>
-      </c>
-      <c r="H27" s="5">
-        <v>29.675889999999999</v>
-      </c>
-      <c r="I27" s="6">
-        <v>-85.333709999999996</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="L27" s="2">
-        <v>4</v>
-      </c>
-      <c r="M27" s="6">
-        <v>29.68289</v>
-      </c>
-      <c r="N27" s="6">
-        <v>-85.307140000000004</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3439,16 +3389,16 @@
         <v>127</v>
       </c>
       <c r="L28" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M28" s="6">
-        <v>29.682110000000002</v>
+        <v>29.68289</v>
       </c>
       <c r="N28" s="6">
-        <v>-85.312110000000004</v>
+        <v>-85.307140000000004</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>129</v>
@@ -3489,19 +3439,19 @@
         <v>127</v>
       </c>
       <c r="L29" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M29" s="6">
-        <v>29.680340000000001</v>
+        <v>29.682110000000002</v>
       </c>
       <c r="N29" s="6">
-        <v>-85.319940000000003</v>
+        <v>-85.312110000000004</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3539,24 +3489,24 @@
         <v>127</v>
       </c>
       <c r="L30" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M30" s="6">
-        <v>29.677489999999999</v>
+        <v>29.680340000000001</v>
       </c>
       <c r="N30" s="6">
-        <v>-85.329430000000002</v>
+        <v>-85.319940000000003</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="11">
-        <v>42046</v>
+        <v>42045</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>123</v>
@@ -3565,98 +3515,98 @@
         <v>124</v>
       </c>
       <c r="D31" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="5">
+        <v>29.683039999999998</v>
+      </c>
+      <c r="G31" s="5">
+        <v>-85.222189999999998</v>
+      </c>
+      <c r="H31" s="5">
+        <v>29.675889999999999</v>
+      </c>
+      <c r="I31" s="6">
+        <v>-85.333709999999996</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L31" s="2">
+        <v>7</v>
+      </c>
+      <c r="M31" s="6">
+        <v>29.677489999999999</v>
+      </c>
+      <c r="N31" s="6">
+        <v>-85.329430000000002</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="11">
+        <v>42046</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E32" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F32" s="5">
         <v>29.698650000000001</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G32" s="5">
         <v>-85.315399999999997</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H32" s="5">
         <v>29.679220000000001</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I32" s="6">
         <v>-85.363879999999995</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L32" s="2">
         <v>2</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M32" s="6">
         <v>29.693619999999999</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N32" s="6">
         <v>-85.312569999999994</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="O32" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13">
-        <v>42043</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F32" s="7">
-        <v>26.669090000000001</v>
-      </c>
-      <c r="G32" s="7">
-        <v>-82.25515</v>
-      </c>
-      <c r="H32" s="2">
-        <v>26.635149999999999</v>
-      </c>
-      <c r="I32" s="2">
-        <v>-82.253245000000007</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L32" s="2">
-        <v>1</v>
-      </c>
-      <c r="M32" s="2">
-        <v>26.669090000000001</v>
-      </c>
-      <c r="N32" s="2">
-        <v>-82.25515</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13">
-        <v>42041</v>
+        <v>42043</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>141</v>
@@ -3665,143 +3615,143 @@
         <v>142</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>144</v>
       </c>
       <c r="F33" s="7">
-        <v>26.465730000000001</v>
+        <v>26.669090000000001</v>
       </c>
       <c r="G33" s="7">
-        <v>-81.967579999999998</v>
+        <v>-82.25515</v>
       </c>
       <c r="H33" s="2">
-        <v>26.4421</v>
+        <v>26.635149999999999</v>
       </c>
       <c r="I33" s="2">
-        <v>-81.931790000000007</v>
+        <v>-82.253245000000007</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="L33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2">
-        <v>26.465730000000001</v>
+        <v>26.669090000000001</v>
       </c>
       <c r="N33" s="2">
-        <v>-81.967579999999998</v>
+        <v>-82.25515</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="13">
-        <v>42042</v>
+        <v>42041</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>144</v>
       </c>
       <c r="F34" s="7">
+        <v>26.465730000000001</v>
+      </c>
+      <c r="G34" s="7">
+        <v>-81.967579999999998</v>
+      </c>
+      <c r="H34" s="2">
+        <v>26.4421</v>
+      </c>
+      <c r="I34" s="2">
+        <v>-81.931790000000007</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L34" s="2">
+        <v>2</v>
+      </c>
+      <c r="M34" s="2">
+        <v>26.465730000000001</v>
+      </c>
+      <c r="N34" s="2">
+        <v>-81.967579999999998</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="13">
+        <v>42042</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" s="7">
         <v>26.479676999999999</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G35" s="7">
         <v>-81.982684000000006</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H35" s="2">
         <v>26.467461</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I35" s="2">
         <v>-81.956676999999999</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L35" s="2">
         <v>1</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M35" s="2">
         <v>26.477371999999999</v>
       </c>
-      <c r="N34" s="2">
+      <c r="N35" s="2">
         <v>-81.970590999999999</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="P34" s="6" t="s">
+      <c r="P35" s="6" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="11">
-        <v>42042</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F35" s="5">
-        <v>-29.135940000000002</v>
-      </c>
-      <c r="G35" s="5">
-        <v>-83.030021000000005</v>
-      </c>
-      <c r="H35" s="5">
-        <v>29.189145</v>
-      </c>
-      <c r="I35" s="6">
-        <v>-83.084327000000002</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L35" s="2">
-        <v>3</v>
-      </c>
-      <c r="M35" s="6">
-        <v>29.155982000000002</v>
-      </c>
-      <c r="N35" s="6">
-        <v>-83.066770000000005</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3839,116 +3789,116 @@
         <v>166</v>
       </c>
       <c r="L36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36" s="6">
-        <v>29.143642</v>
+        <v>29.155982000000002</v>
       </c>
       <c r="N36" s="6">
-        <v>-83.064563000000007</v>
+        <v>-83.066770000000005</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="11">
-        <v>42045</v>
+        <v>42042</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>178</v>
+        <v>164</v>
+      </c>
+      <c r="F37" s="5">
+        <v>-29.135940000000002</v>
+      </c>
+      <c r="G37" s="5">
+        <v>-83.030021000000005</v>
+      </c>
+      <c r="H37" s="5">
+        <v>29.189145</v>
+      </c>
+      <c r="I37" s="6">
+        <v>-83.084327000000002</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="L37" s="2">
-        <v>5</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="N37" s="6" t="s">
-        <v>182</v>
+        <v>4</v>
+      </c>
+      <c r="M37" s="6">
+        <v>29.143642</v>
+      </c>
+      <c r="N37" s="6">
+        <v>-83.064563000000007</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>109</v>
+        <v>169</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="11">
-        <v>42044</v>
+        <v>42045</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F38" s="5">
-        <v>25.700642999999999</v>
-      </c>
-      <c r="G38" s="5">
-        <v>-80.154668000000001</v>
-      </c>
-      <c r="H38" s="5">
-        <v>25.724667</v>
-      </c>
-      <c r="I38" s="6">
-        <v>-80.147873000000004</v>
+        <v>174</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="M38" s="6">
-        <v>25.701205000000002</v>
-      </c>
-      <c r="N38" s="6">
-        <v>-80.154668000000001</v>
+        <v>180</v>
+      </c>
+      <c r="L38" s="2">
+        <v>5</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>182</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>191</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3968,37 +3918,37 @@
         <v>186</v>
       </c>
       <c r="F39" s="5">
-        <v>25.70064</v>
+        <v>25.700642999999999</v>
       </c>
       <c r="G39" s="5">
-        <v>-80.154669999999996</v>
+        <v>-80.154668000000001</v>
       </c>
       <c r="H39" s="5">
-        <v>25.72467</v>
+        <v>25.724667</v>
       </c>
       <c r="I39" s="6">
-        <v>-80.147869999999998</v>
+        <v>-80.147873000000004</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>188</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M39" s="6">
-        <v>25.700689000000001</v>
+        <v>25.701205000000002</v>
       </c>
       <c r="N39" s="6">
-        <v>-80.154995</v>
+        <v>-80.154668000000001</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4036,119 +3986,119 @@
         <v>188</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M40" s="6">
-        <v>25.702079999999999</v>
+        <v>25.700689000000001</v>
       </c>
       <c r="N40" s="6">
-        <v>-80.154334000000006</v>
+        <v>-80.154995</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="11">
-        <v>42046</v>
+        <v>42044</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="F41" s="5">
-        <v>24.537579999999998</v>
+        <v>25.70064</v>
       </c>
       <c r="G41" s="5">
-        <v>-82.008179999999996</v>
+        <v>-80.154669999999996</v>
       </c>
       <c r="H41" s="5">
-        <v>24.527509999999999</v>
+        <v>25.72467</v>
       </c>
       <c r="I41" s="6">
-        <v>-82.006290000000007</v>
+        <v>-80.147869999999998</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="L41" s="2">
-        <v>1</v>
+        <v>188</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="M41" s="6">
-        <v>24.53105</v>
+        <v>25.702079999999999</v>
       </c>
       <c r="N41" s="6">
-        <v>-82.007639999999995</v>
+        <v>-80.154334000000006</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>65</v>
+        <v>197</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="11">
-        <v>42041</v>
+        <v>42046</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F42" s="5">
-        <v>28.229900000000001</v>
+        <v>24.537579999999998</v>
       </c>
       <c r="G42" s="5">
-        <v>-82.840169000000003</v>
+        <v>-82.008179999999996</v>
       </c>
       <c r="H42" s="5">
-        <v>28.229900000000001</v>
-      </c>
-      <c r="I42" s="5">
-        <v>-82.840169000000003</v>
+        <v>24.527509999999999</v>
+      </c>
+      <c r="I42" s="6">
+        <v>-82.006290000000007</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="L42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" s="6">
-        <v>28.234629999999999</v>
+        <v>24.53105</v>
       </c>
       <c r="N42" s="6">
-        <v>-82.837199999999996</v>
+        <v>-82.007639999999995</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>212</v>
+        <v>65</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4156,46 +4106,49 @@
         <v>42041</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="F43" s="6">
-        <v>28.13167</v>
+        <v>209</v>
+      </c>
+      <c r="F43" s="5">
+        <v>28.229900000000001</v>
       </c>
       <c r="G43" s="5">
-        <v>-82.828010000000006</v>
+        <v>-82.840169000000003</v>
       </c>
       <c r="H43" s="5">
-        <v>28.112490000000001</v>
+        <v>28.229900000000001</v>
       </c>
       <c r="I43" s="5">
-        <v>-82.838549999999998</v>
+        <v>-82.840169000000003</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="L43" s="2">
         <v>2</v>
       </c>
       <c r="M43" s="6">
-        <v>28.1309</v>
+        <v>28.234629999999999</v>
       </c>
       <c r="N43" s="6">
-        <v>-82.829279999999997</v>
+        <v>-82.837199999999996</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>109</v>
+        <v>212</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4233,16 +4186,16 @@
         <v>219</v>
       </c>
       <c r="L44" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M44" s="6">
-        <v>28.130420000000001</v>
+        <v>28.1309</v>
       </c>
       <c r="N44" s="6">
-        <v>-82.830380000000005</v>
+        <v>-82.829279999999997</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4280,16 +4233,16 @@
         <v>219</v>
       </c>
       <c r="L45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M45" s="6">
-        <v>28.12978</v>
+        <v>28.130420000000001</v>
       </c>
       <c r="N45" s="6">
-        <v>-82.831850000000003</v>
+        <v>-82.830380000000005</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4327,16 +4280,16 @@
         <v>219</v>
       </c>
       <c r="L46" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M46" s="6">
-        <v>28.12857</v>
+        <v>28.12978</v>
       </c>
       <c r="N46" s="6">
-        <v>-82.833780000000004</v>
+        <v>-82.831850000000003</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>109</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4374,19 +4327,16 @@
         <v>219</v>
       </c>
       <c r="L47" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M47" s="6">
-        <v>28.12717</v>
+        <v>28.12857</v>
       </c>
       <c r="N47" s="6">
-        <v>-82.83511</v>
+        <v>-82.833780000000004</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>223</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4424,19 +4374,19 @@
         <v>219</v>
       </c>
       <c r="L48" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M48" s="6">
-        <v>28.125900000000001</v>
+        <v>28.12717</v>
       </c>
       <c r="N48" s="6">
-        <v>-82.836420000000004</v>
+        <v>-82.83511</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4474,16 +4424,19 @@
         <v>219</v>
       </c>
       <c r="L49" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M49" s="6">
-        <v>28.125209999999999</v>
+        <v>28.125900000000001</v>
       </c>
       <c r="N49" s="6">
-        <v>-82.83672</v>
+        <v>-82.836420000000004</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>224</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4521,19 +4474,16 @@
         <v>219</v>
       </c>
       <c r="L50" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M50" s="6">
-        <v>28.118359999999999</v>
+        <v>28.125209999999999</v>
       </c>
       <c r="N50" s="6">
-        <v>-82.838589999999996</v>
+        <v>-82.83672</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4571,13 +4521,13 @@
         <v>219</v>
       </c>
       <c r="L51" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M51" s="6">
-        <v>28.117380000000001</v>
+        <v>28.118359999999999</v>
       </c>
       <c r="N51" s="6">
-        <v>-82.838669999999993</v>
+        <v>-82.838589999999996</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>226</v>
@@ -4621,13 +4571,13 @@
         <v>219</v>
       </c>
       <c r="L52" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M52" s="6">
-        <v>28.115739999999999</v>
+        <v>28.117380000000001</v>
       </c>
       <c r="N52" s="6">
-        <v>-82.838679999999997</v>
+        <v>-82.838669999999993</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>226</v>
@@ -4671,16 +4621,19 @@
         <v>219</v>
       </c>
       <c r="L53" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M53" s="6">
-        <v>28.114529999999998</v>
+        <v>28.115739999999999</v>
       </c>
       <c r="N53" s="6">
-        <v>-82.838530000000006</v>
+        <v>-82.838679999999997</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4688,49 +4641,46 @@
         <v>42041</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="F54" s="5">
-        <v>28.06578</v>
+      <c r="F54" s="6">
+        <v>28.13167</v>
       </c>
       <c r="G54" s="5">
-        <v>-82.833420000000004</v>
+        <v>-82.828010000000006</v>
       </c>
       <c r="H54" s="5">
-        <v>28.093816</v>
-      </c>
-      <c r="I54" s="6">
-        <v>-82.833689000000007</v>
+        <v>28.112490000000001</v>
+      </c>
+      <c r="I54" s="5">
+        <v>-82.838549999999998</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="L54" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M54" s="6">
-        <v>28.094142999999999</v>
+        <v>28.114529999999998</v>
       </c>
       <c r="N54" s="6">
-        <v>-82.833699999999993</v>
+        <v>-82.838530000000006</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4738,31 +4688,31 @@
         <v>42041</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>217</v>
       </c>
       <c r="F55" s="5">
-        <v>28.165891999999999</v>
+        <v>28.06578</v>
       </c>
       <c r="G55" s="5">
-        <v>-82.840677999999997</v>
+        <v>-82.833420000000004</v>
       </c>
       <c r="H55" s="5">
-        <v>28.171811000000002</v>
+        <v>28.093816</v>
       </c>
       <c r="I55" s="6">
-        <v>-82.849756999999997</v>
+        <v>-82.833689000000007</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>211</v>
@@ -4771,16 +4721,16 @@
         <v>1</v>
       </c>
       <c r="M55" s="6">
-        <v>28.162769999999998</v>
+        <v>28.094142999999999</v>
       </c>
       <c r="N55" s="6">
-        <v>-82.84496</v>
+        <v>-82.833699999999993</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4818,119 +4768,119 @@
         <v>211</v>
       </c>
       <c r="L56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" s="6">
-        <v>28.159700000000001</v>
+        <v>28.162769999999998</v>
       </c>
       <c r="N56" s="6">
-        <v>-82.840180000000004</v>
+        <v>-82.84496</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="11">
-        <v>42042</v>
+        <v>42041</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>248</v>
+      <c r="F57" s="5">
+        <v>28.165891999999999</v>
+      </c>
+      <c r="G57" s="5">
+        <v>-82.840677999999997</v>
+      </c>
+      <c r="H57" s="5">
+        <v>28.171811000000002</v>
+      </c>
+      <c r="I57" s="6">
+        <v>-82.849756999999997</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="L57" s="2">
-        <v>13</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="N57" s="6" t="s">
-        <v>251</v>
+        <v>2</v>
+      </c>
+      <c r="M57" s="6">
+        <v>28.159700000000001</v>
+      </c>
+      <c r="N57" s="6">
+        <v>-82.840180000000004</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="11">
-        <v>42041</v>
+        <v>42042</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="F58" s="5">
-        <v>28.105</v>
-      </c>
-      <c r="G58" s="5">
-        <v>-82.828090000000003</v>
-      </c>
-      <c r="H58" s="5">
-        <v>28.111979999999999</v>
-      </c>
-      <c r="I58" s="6">
-        <v>-82.837299999999999</v>
+      <c r="F58" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="L58" s="2">
-        <v>3</v>
-      </c>
-      <c r="M58" s="6">
-        <v>28.11158</v>
-      </c>
-      <c r="N58" s="6">
-        <v>-82.837019999999995</v>
+        <v>13</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4968,19 +4918,19 @@
         <v>258</v>
       </c>
       <c r="L59" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M59" s="6">
-        <v>28.10613</v>
+        <v>28.11158</v>
       </c>
       <c r="N59" s="6">
-        <v>-82.833349999999996</v>
+        <v>-82.837019999999995</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5003,13 +4953,13 @@
         <v>28.105</v>
       </c>
       <c r="G60" s="5">
-        <v>82.828090000000003</v>
+        <v>-82.828090000000003</v>
       </c>
       <c r="H60" s="5">
         <v>28.111979999999999</v>
       </c>
       <c r="I60" s="6">
-        <v>82.837299999999999</v>
+        <v>-82.837299999999999</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>257</v>
@@ -5018,19 +4968,19 @@
         <v>258</v>
       </c>
       <c r="L60" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M60" s="6">
-        <v>28.105979999999999</v>
+        <v>28.10613</v>
       </c>
       <c r="N60" s="6">
-        <v>-82.835070000000002</v>
+        <v>-82.833349999999996</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5038,49 +4988,49 @@
         <v>42041</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="F61" s="5">
-        <v>30.351009999999999</v>
+        <v>28.105</v>
       </c>
       <c r="G61" s="5">
-        <v>-87.071150000000003</v>
+        <v>82.828090000000003</v>
       </c>
       <c r="H61" s="5">
-        <v>30.355799999999999</v>
+        <v>28.111979999999999</v>
       </c>
       <c r="I61" s="6">
-        <v>-87.042519999999996</v>
+        <v>82.837299999999999</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="L61" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M61" s="6">
-        <v>30.35707</v>
+        <v>28.105979999999999</v>
       </c>
       <c r="N61" s="6">
-        <v>-87.047650000000004</v>
+        <v>-82.835070000000002</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5118,19 +5068,19 @@
         <v>270</v>
       </c>
       <c r="L62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="6">
-        <v>30.357430000000001</v>
+        <v>30.35707</v>
       </c>
       <c r="N62" s="6">
-        <v>-87.043610000000001</v>
+        <v>-87.047650000000004</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5144,93 +5094,93 @@
         <v>266</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>268</v>
       </c>
       <c r="F63" s="5">
-        <v>30.379349999999999</v>
+        <v>30.351009999999999</v>
       </c>
       <c r="G63" s="5">
-        <v>-86.863609999999994</v>
+        <v>-87.071150000000003</v>
       </c>
       <c r="H63" s="5">
-        <v>30.386150000000001</v>
+        <v>30.355799999999999</v>
       </c>
       <c r="I63" s="6">
-        <v>-86.849930000000001</v>
+        <v>-87.042519999999996</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="L63" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M63" s="6">
-        <v>30.385950000000001</v>
+        <v>30.357430000000001</v>
       </c>
       <c r="N63" s="6">
-        <v>-86.868535699999995</v>
+        <v>-87.043610000000001</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="11">
-        <v>42045</v>
+        <v>42041</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="F64" s="5">
-        <v>29.076041</v>
+        <v>30.379349999999999</v>
       </c>
       <c r="G64" s="5">
-        <v>-80.925753999999998</v>
+        <v>-86.863609999999994</v>
       </c>
       <c r="H64" s="5">
-        <v>29.062266000000001</v>
+        <v>30.386150000000001</v>
       </c>
       <c r="I64" s="6">
-        <v>-80.918727000000004</v>
+        <v>-86.849930000000001</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="L64" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M64" s="6">
-        <v>29.068829999999998</v>
+        <v>30.385950000000001</v>
       </c>
       <c r="N64" s="6">
-        <v>-80.926526999999993</v>
+        <v>-86.868535699999995</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5268,16 +5218,16 @@
         <v>285</v>
       </c>
       <c r="L65" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M65" s="6">
-        <v>29.069133999999998</v>
+        <v>29.068829999999998</v>
       </c>
       <c r="N65" s="6">
-        <v>-80.925488000000001</v>
+        <v>-80.926526999999993</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>287</v>
@@ -5318,19 +5268,19 @@
         <v>285</v>
       </c>
       <c r="L66" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M66" s="6">
-        <v>29.069884999999999</v>
+        <v>29.069133999999998</v>
       </c>
       <c r="N66" s="6">
-        <v>-80.925815999999998</v>
+        <v>-80.925488000000001</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5368,19 +5318,19 @@
         <v>285</v>
       </c>
       <c r="L67" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M67" s="6">
-        <v>29.070111000000001</v>
+        <v>29.069884999999999</v>
       </c>
       <c r="N67" s="6">
-        <v>-80.926293999999999</v>
+        <v>-80.925815999999998</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5418,19 +5368,19 @@
         <v>285</v>
       </c>
       <c r="L68" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M68" s="6">
-        <v>29.072016999999999</v>
+        <v>29.070111000000001</v>
       </c>
       <c r="N68" s="6">
-        <v>-80.928044</v>
+        <v>-80.926293999999999</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5438,96 +5388,99 @@
         <v>42045</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>283</v>
       </c>
       <c r="F69" s="5">
+        <v>29.076041</v>
+      </c>
+      <c r="G69" s="5">
+        <v>-80.925753999999998</v>
+      </c>
+      <c r="H69" s="5">
+        <v>29.062266000000001</v>
+      </c>
+      <c r="I69" s="6">
+        <v>-80.918727000000004</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="L69" s="2">
+        <v>9</v>
+      </c>
+      <c r="M69" s="6">
+        <v>29.072016999999999</v>
+      </c>
+      <c r="N69" s="6">
+        <v>-80.928044</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="11">
+        <v>42045</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F70" s="5">
         <v>29.078524999999999</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G70" s="5">
         <v>80.918942000000001</v>
       </c>
-      <c r="H69" s="5">
+      <c r="H70" s="5">
         <v>29.472049999999999</v>
       </c>
-      <c r="I69" s="6">
+      <c r="I70" s="6">
         <v>81.102138999999994</v>
       </c>
-      <c r="J69" s="2" t="s">
+      <c r="J70" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="K69" s="2" t="s">
+      <c r="K70" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="L69" s="2">
-        <v>1</v>
-      </c>
-      <c r="M69" s="6">
-        <v>29.081666999999999</v>
-      </c>
-      <c r="N69" s="6">
-        <v>80.921389000000005</v>
-      </c>
-      <c r="O69" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="P69" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="4">
-        <v>42041</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F70" s="2">
-        <v>30.355328</v>
-      </c>
-      <c r="G70" s="2">
-        <v>-87.035578000000001</v>
-      </c>
-      <c r="H70" s="2">
-        <v>30.3520322</v>
-      </c>
-      <c r="I70" s="6">
-        <v>-87.044630999999995</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="L70" s="2">
         <v>1</v>
       </c>
-      <c r="M70" s="2">
-        <v>30.355967</v>
-      </c>
-      <c r="N70" s="2">
-        <v>-87.043892</v>
+      <c r="M70" s="6">
+        <v>29.081666999999999</v>
+      </c>
+      <c r="N70" s="6">
+        <v>80.921389000000005</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>220</v>
+        <v>49</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5565,20 +5518,66 @@
         <v>304</v>
       </c>
       <c r="L71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2">
-        <v>30.356508000000002</v>
+        <v>30.355967</v>
       </c>
       <c r="N71" s="2">
-        <v>-87.043953000000002</v>
+        <v>-87.043892</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="P71" s="6"/>
-    </row>
-    <row r="72" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    </row>
+    <row r="72" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="4">
+        <v>42041</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F72" s="2">
+        <v>30.355328</v>
+      </c>
+      <c r="G72" s="2">
+        <v>-87.035578000000001</v>
+      </c>
+      <c r="H72" s="2">
+        <v>30.3520322</v>
+      </c>
+      <c r="I72" s="6">
+        <v>-87.044630999999995</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L72" s="2">
+        <v>2</v>
+      </c>
+      <c r="M72" s="2">
+        <v>30.356508000000002</v>
+      </c>
+      <c r="N72" s="2">
+        <v>-87.043953000000002</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="P72" s="6"/>
+    </row>
     <row r="73" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="74" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="75" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -6165,9 +6164,10 @@
     <row r="656" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="657" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="658" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6196,16 +6196,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>305</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="E1" s="27"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
-      <c r="H1" s="27"/>
+      <c r="H1" s="26"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
       <c r="K1" s="25"/>
